--- a/outputs/reports/oncology_registry_report.xlsx
+++ b/outputs/reports/oncology_registry_report.xlsx
@@ -59,7 +59,7 @@
     <t>Aggregated quality and activity report for the oncology clinical registry demonstration project.</t>
   </si>
   <si>
-    <t>2026-08-05T21:26:53+00:00</t>
+    <t>2026-08-06T00:09:07+00:00</t>
   </si>
   <si>
     <t>data/processed/oncology_registry_validated.csv</t>

--- a/outputs/reports/oncology_registry_report.xlsx
+++ b/outputs/reports/oncology_registry_report.xlsx
@@ -59,7 +59,7 @@
     <t>Aggregated quality and activity report for the oncology clinical registry demonstration project.</t>
   </si>
   <si>
-    <t>2026-08-06T00:09:07+00:00</t>
+    <t>2026-08-06T16:26:41+00:00</t>
   </si>
   <si>
     <t>data/processed/oncology_registry_validated.csv</t>
